--- a/skillbox/2.6 Case Filled.xlsx
+++ b/skillbox/2.6 Case Filled.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\economics\udemy_economics\skillbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3CB4F2-40A3-4023-A6BD-BEC847E9CCB1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088A4454-9B6D-4B86-93DC-E024D12912AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="81">
   <si>
     <t>БАЛАНС</t>
   </si>
@@ -252,6 +252,30 @@
   </si>
   <si>
     <t>Швидка ліквідність</t>
+  </si>
+  <si>
+    <t>Обертаємість дебіторської заборгованості</t>
+  </si>
+  <si>
+    <t>Обертаємість запасів</t>
+  </si>
+  <si>
+    <t>Обертаємість кредіторської заборгованості</t>
+  </si>
+  <si>
+    <t>Обертаємість постійних активів</t>
+  </si>
+  <si>
+    <t>Фінансовий важіль</t>
+  </si>
+  <si>
+    <t>Коефіціент фінансової незалежності</t>
+  </si>
+  <si>
+    <t>Сумарний борг</t>
+  </si>
+  <si>
+    <t>TD/EBITDA</t>
   </si>
 </sst>
 </file>
@@ -685,7 +709,7 @@
     <col min="1" max="1" width="39.5546875" customWidth="1"/>
     <col min="2" max="4" width="12.5546875" customWidth="1"/>
     <col min="5" max="5" width="2.44140625" customWidth="1"/>
-    <col min="6" max="6" width="34.5546875" customWidth="1"/>
+    <col min="6" max="6" width="38.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="12.5546875" customWidth="1"/>
     <col min="10" max="26" width="8.6640625" customWidth="1"/>
   </cols>
@@ -758,9 +782,21 @@
       <c r="D5" s="8">
         <v>0</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
+      <c r="F5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" s="9">
+        <f>B14/B40*365</f>
+        <v>56.509768268844084</v>
+      </c>
+      <c r="H5" s="9">
+        <f>C14/C40*365</f>
+        <v>27.954386483020677</v>
+      </c>
+      <c r="I5" s="9">
+        <f>D14/D40*365</f>
+        <v>2.9614224331997354</v>
+      </c>
     </row>
     <row r="6" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -775,9 +811,21 @@
       <c r="D6" s="8">
         <v>188542</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
+      <c r="F6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="9">
+        <f>SUM(B11,B12,B13)/B40*365</f>
+        <v>28.283936681881571</v>
+      </c>
+      <c r="H6" s="9">
+        <f>SUM(C11,C12,C13)/C40*365</f>
+        <v>19.219517289237935</v>
+      </c>
+      <c r="I6" s="9">
+        <f>SUM(D11,D12,D13)/D40*365</f>
+        <v>21.571478109289597</v>
+      </c>
     </row>
     <row r="7" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
@@ -792,9 +840,21 @@
       <c r="D7" s="8">
         <v>167750</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
+      <c r="F7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="9">
+        <f>B33/B40*365</f>
+        <v>45.940622400407264</v>
+      </c>
+      <c r="H7" s="9">
+        <f>C33/C40*365</f>
+        <v>55.849769918500165</v>
+      </c>
+      <c r="I7" s="9">
+        <f>D33/D40*365</f>
+        <v>92.622932024880086</v>
+      </c>
     </row>
     <row r="8" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -809,24 +869,36 @@
       <c r="D8" s="8">
         <v>15615</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="F8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="9">
+        <f>B40/B9</f>
+        <v>3.5005841769341819</v>
+      </c>
+      <c r="H8" s="9">
+        <f t="shared" ref="H8:I8" si="0">C40/C9</f>
+        <v>2.1577291860085284</v>
+      </c>
+      <c r="I8" s="9">
+        <f t="shared" si="0"/>
+        <v>1.3411932352506755</v>
+      </c>
     </row>
     <row r="9" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="11">
-        <f t="shared" ref="B9:D9" si="0">SUM(B5:B8)</f>
+        <f t="shared" ref="B9:D9" si="1">SUM(B5:B8)</f>
         <v>244049</v>
       </c>
       <c r="C9" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>349769</v>
       </c>
       <c r="D9" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>371907</v>
       </c>
     </row>
@@ -954,15 +1026,15 @@
         <v>14</v>
       </c>
       <c r="B19" s="11">
-        <f t="shared" ref="B19:D19" si="1">SUM(B11:B18)</f>
+        <f t="shared" ref="B19:D19" si="2">SUM(B11:B18)</f>
         <v>257566</v>
       </c>
       <c r="C19" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>127045</v>
       </c>
       <c r="D19" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>41618</v>
       </c>
       <c r="F19" t="s">
@@ -1007,15 +1079,15 @@
         <v>15</v>
       </c>
       <c r="B21" s="17">
-        <f t="shared" ref="B21:D21" si="2">B19+B9</f>
+        <f t="shared" ref="B21:D21" si="3">B19+B9</f>
         <v>501615</v>
       </c>
       <c r="C21" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>476814</v>
       </c>
       <c r="D21" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>413525</v>
       </c>
       <c r="F21" t="s">
@@ -1087,15 +1159,15 @@
         <v>19</v>
       </c>
       <c r="B26" s="11">
-        <f t="shared" ref="B26:D26" si="3">SUM(B23:B25)</f>
+        <f t="shared" ref="B26:D26" si="4">SUM(B23:B25)</f>
         <v>30372</v>
       </c>
       <c r="C26" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4204</v>
       </c>
       <c r="D26" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>62</v>
       </c>
     </row>
@@ -1119,9 +1191,21 @@
       <c r="D28" s="8">
         <v>178058</v>
       </c>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
+      <c r="F28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="18">
+        <f>B21/B26</f>
+        <v>16.515705254839983</v>
+      </c>
+      <c r="H28" s="18">
+        <f>C21/C26</f>
+        <v>113.41912464319695</v>
+      </c>
+      <c r="I28" s="18">
+        <f>D21/D26</f>
+        <v>6669.7580645161288</v>
+      </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
@@ -1136,38 +1220,74 @@
       <c r="D29" s="8">
         <v>1993</v>
       </c>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
+      <c r="F29" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" s="19">
+        <f>B26/B21</f>
+        <v>6.0548428575700489E-2</v>
+      </c>
+      <c r="H29" s="19">
+        <f>C26/C21</f>
+        <v>8.8168552097883032E-3</v>
+      </c>
+      <c r="I29" s="19">
+        <f>D26/D21</f>
+        <v>1.4993047578743728E-4</v>
+      </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>22</v>
       </c>
       <c r="B30" s="11">
-        <f t="shared" ref="B30:D30" si="4">SUM(B28:B29)</f>
+        <f t="shared" ref="B30:D30" si="5">SUM(B28:B29)</f>
         <v>291593</v>
       </c>
       <c r="C30" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>258380</v>
       </c>
       <c r="D30" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>180051</v>
       </c>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
+      <c r="F30" t="s">
+        <v>79</v>
+      </c>
+      <c r="G30" s="14">
+        <f>B28+B32</f>
+        <v>361310</v>
+      </c>
+      <c r="H30" s="14">
+        <f>C28+C32</f>
+        <v>355590</v>
+      </c>
+      <c r="I30" s="14">
+        <f>D28+D32</f>
+        <v>284801</v>
+      </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="12"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
+      <c r="F31" t="s">
+        <v>80</v>
+      </c>
+      <c r="G31" s="9">
+        <f>G30/B50</f>
+        <v>-8.0962320769285423</v>
+      </c>
+      <c r="H31" s="9">
+        <f>H30/C50</f>
+        <v>12.056849306408786</v>
+      </c>
+      <c r="I31" s="9">
+        <f>I30/D50</f>
+        <v>5.5332159070178468</v>
+      </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
@@ -1202,15 +1322,15 @@
         <v>25</v>
       </c>
       <c r="B34" s="11">
-        <f t="shared" ref="B34:D34" si="5">SUM(B32:B33)</f>
+        <f t="shared" ref="B34:D34" si="6">SUM(B32:B33)</f>
         <v>179650</v>
       </c>
       <c r="C34" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>214230</v>
       </c>
       <c r="D34" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>233319</v>
       </c>
     </row>
@@ -1225,15 +1345,15 @@
         <v>26</v>
       </c>
       <c r="B36" s="17">
-        <f t="shared" ref="B36:D36" si="6">B26+B30+B34</f>
+        <f t="shared" ref="B36:D36" si="7">B26+B30+B34</f>
         <v>501615</v>
       </c>
       <c r="C36" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>476814</v>
       </c>
       <c r="D36" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>413432</v>
       </c>
     </row>
@@ -1281,15 +1401,15 @@
         <v>29</v>
       </c>
       <c r="G40" s="19">
-        <f t="shared" ref="G40:I40" si="7">B60/B40</f>
+        <f t="shared" ref="G40:I40" si="8">B60/B40</f>
         <v>-4.9301461594820906E-2</v>
       </c>
       <c r="H40" s="19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-2.466550035146654E-2</v>
       </c>
       <c r="I40" s="19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.2072129164451916E-3</v>
       </c>
     </row>
@@ -1310,15 +1430,15 @@
         <v>31</v>
       </c>
       <c r="G41" s="19">
-        <f t="shared" ref="G41:I41" si="8">B50/B40</f>
+        <f t="shared" ref="G41:I41" si="9">B50/B40</f>
         <v>-5.2237150113293378E-2</v>
       </c>
       <c r="H41" s="19">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.9078461272421504E-2</v>
       </c>
       <c r="I41" s="19">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10319013631042701</v>
       </c>
     </row>
@@ -1339,15 +1459,15 @@
         <v>33</v>
       </c>
       <c r="G42" s="19">
-        <f t="shared" ref="G42:I42" si="9">B60/B21</f>
+        <f t="shared" ref="G42:I42" si="10">B60/B21</f>
         <v>-8.3966652120430613E-2</v>
       </c>
       <c r="H42" s="19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-3.9040842632521271E-2</v>
       </c>
       <c r="I42" s="19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.4872197385235052E-3</v>
       </c>
     </row>
@@ -1368,15 +1488,15 @@
         <v>35</v>
       </c>
       <c r="G43" s="19">
-        <f t="shared" ref="G43:I43" si="10">B60/B26</f>
+        <f t="shared" ref="G43:I43" si="11">B60/B26</f>
         <v>-1.3867684776567166</v>
       </c>
       <c r="H43" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-4.4279781967133669</v>
       </c>
       <c r="I43" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>49.937944231821497</v>
       </c>
     </row>

--- a/skillbox/2.6 Case Filled.xlsx
+++ b/skillbox/2.6 Case Filled.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\economics\udemy_economics\skillbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088A4454-9B6D-4B86-93DC-E024D12912AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBDD873-0DED-407F-BF3C-58C84D225471}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="82">
   <si>
     <t>БАЛАНС</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>TD/EBITDA</t>
+  </si>
+  <si>
+    <t>Операційний важіль</t>
   </si>
 </sst>
 </file>
@@ -1513,9 +1516,21 @@
       <c r="D44" s="8">
         <v>-61302</v>
       </c>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
+      <c r="F44" t="s">
+        <v>81</v>
+      </c>
+      <c r="G44" s="9">
+        <f>(B41+B47+B48+B49)/B42</f>
+        <v>2.2222222222222223</v>
+      </c>
+      <c r="H44" s="9">
+        <f>(C41+C47+C48+C49)/C42</f>
+        <v>2.1276595744680851</v>
+      </c>
+      <c r="I44" s="9">
+        <f>(D41+D47+D48+D49)/D42</f>
+        <v>2.1849122035802377</v>
+      </c>
     </row>
     <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">

--- a/skillbox/2.6 Case Filled.xlsx
+++ b/skillbox/2.6 Case Filled.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\economics\udemy_economics\skillbox\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBDD873-0DED-407F-BF3C-58C84D225471}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14505" yWindow="-15" windowWidth="14310" windowHeight="6420"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1 (2)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -284,7 +278,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -423,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -491,6 +485,7 @@
     <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -705,19 +700,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.5546875" customWidth="1"/>
-    <col min="2" max="4" width="12.5546875" customWidth="1"/>
-    <col min="5" max="5" width="2.44140625" customWidth="1"/>
-    <col min="6" max="6" width="38.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="12.5546875" customWidth="1"/>
-    <col min="10" max="26" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="39.5703125" customWidth="1"/>
+    <col min="2" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="2.42578125" customWidth="1"/>
+    <col min="6" max="6" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="12.5703125" customWidth="1"/>
+    <col min="10" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1">
         <v>2017</v>
@@ -751,7 +746,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -765,14 +760,14 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
@@ -801,7 +796,7 @@
         <v>2.9614224331997354</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
@@ -830,7 +825,7 @@
         <v>21.571478109289597</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
@@ -859,7 +854,7 @@
         <v>92.622932024880086</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -888,7 +883,7 @@
         <v>1.3411932352506755</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>5</v>
       </c>
@@ -905,13 +900,13 @@
         <v>371907</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
     </row>
-    <row r="11" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
@@ -925,7 +920,7 @@
         <v>26951</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>7</v>
       </c>
@@ -939,7 +934,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
@@ -953,7 +948,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>9</v>
       </c>
@@ -967,7 +962,7 @@
         <v>4047</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>10</v>
       </c>
@@ -981,7 +976,7 @@
         <v>4990</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>11</v>
       </c>
@@ -995,7 +990,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
@@ -1009,7 +1004,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
@@ -1024,7 +1019,7 @@
       </c>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>14</v>
       </c>
@@ -1056,7 +1051,7 @@
         <v>-191701</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -1077,7 +1072,7 @@
         <v>0.17837381439145547</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>15</v>
       </c>
@@ -1109,13 +1104,13 @@
         <v>2.5360129265083426E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
     </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>16</v>
       </c>
@@ -1129,7 +1124,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>17</v>
       </c>
@@ -1143,7 +1138,7 @@
         <v>-96114</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>18</v>
       </c>
@@ -1157,7 +1152,7 @@
         <v>95939</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>19</v>
       </c>
@@ -1174,14 +1169,14 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>20</v>
       </c>
@@ -1210,7 +1205,7 @@
         <v>6669.7580645161288</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>21</v>
       </c>
@@ -1239,7 +1234,7 @@
         <v>1.4993047578743728E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>22</v>
       </c>
@@ -1271,7 +1266,7 @@
         <v>284801</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -1292,7 +1287,7 @@
         <v>5.5332159070178468</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>23</v>
       </c>
@@ -1306,7 +1301,7 @@
         <v>106743</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>24</v>
       </c>
@@ -1320,7 +1315,7 @@
         <v>126576</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>25</v>
       </c>
@@ -1337,13 +1332,13 @@
         <v>233319</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
     </row>
-    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>26</v>
       </c>
@@ -1360,13 +1355,13 @@
         <v>413432</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>27</v>
       </c>
@@ -1380,14 +1375,14 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>28</v>
       </c>
@@ -1416,7 +1411,7 @@
         <v>6.2072129164451916E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>30</v>
       </c>
@@ -1445,7 +1440,7 @@
         <v>0.10319013631042701</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>32</v>
       </c>
@@ -1474,7 +1469,7 @@
         <v>7.4872197385235052E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>34</v>
       </c>
@@ -1503,7 +1498,7 @@
         <v>49.937944231821497</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>36</v>
       </c>
@@ -1532,7 +1527,7 @@
         <v>2.1849122035802377</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>37</v>
       </c>
@@ -1546,13 +1541,13 @@
         <v>147405.15254237293</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
       <c r="D46" s="15"/>
     </row>
-    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>38</v>
       </c>
@@ -1566,7 +1561,7 @@
         <v>-46893</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>39</v>
       </c>
@@ -1580,7 +1575,7 @@
         <v>-26139</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>40</v>
       </c>
@@ -1594,7 +1589,7 @@
         <v>-22902</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>41</v>
       </c>
@@ -1607,14 +1602,18 @@
       <c r="D50" s="11">
         <v>51471.152542372933</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F50" s="33">
+        <f>B40+B41+B47+B48+B49</f>
+        <v>-44626.932203389821</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
       <c r="D51" s="15"/>
     </row>
-    <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>42</v>
       </c>
@@ -1628,7 +1627,7 @@
         <v>-10353</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>43</v>
       </c>
@@ -1642,7 +1641,7 @@
         <v>-23145</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>44</v>
       </c>
@@ -1656,13 +1655,13 @@
         <v>17973.152542372933</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
       <c r="D55" s="15"/>
     </row>
-    <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1675,7 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>46</v>
       </c>
@@ -1690,7 +1689,7 @@
         <v>-35624</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>47</v>
       </c>
@@ -1704,7 +1703,7 @@
         <v>3169.1525423729327</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>48</v>
       </c>
@@ -1718,7 +1717,7 @@
         <v>-73</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>49</v>
       </c>
@@ -1732,951 +1731,951 @@
         <v>3096.1525423729327</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
       <c r="D61" s="15"/>
     </row>
-    <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2684,19 +2683,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.5546875" customWidth="1"/>
-    <col min="2" max="4" width="12.5546875" customWidth="1"/>
-    <col min="5" max="5" width="2.44140625" customWidth="1"/>
-    <col min="6" max="6" width="34.5546875" customWidth="1"/>
-    <col min="7" max="9" width="12.5546875" customWidth="1"/>
-    <col min="10" max="26" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="39.5703125" customWidth="1"/>
+    <col min="2" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="2.42578125" customWidth="1"/>
+    <col min="6" max="6" width="34.5703125" customWidth="1"/>
+    <col min="7" max="9" width="12.5703125" customWidth="1"/>
+    <col min="10" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1">
         <v>2017</v>
@@ -2736,7 +2735,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2750,7 +2749,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2759,7 +2758,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
@@ -2788,7 +2787,7 @@
         <v>6.6128921494504587</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
@@ -2817,7 +2816,7 @@
         <v>21.571478109289597</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
@@ -2846,7 +2845,7 @@
         <v>92.622932024880086</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -2875,7 +2874,7 @@
         <v>1.3411932352506755</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>5</v>
       </c>
@@ -2889,13 +2888,13 @@
         <v>371907</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
     </row>
-    <row r="11" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
@@ -2909,7 +2908,7 @@
         <v>26951</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>7</v>
       </c>
@@ -2923,7 +2922,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
@@ -2937,7 +2936,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>9</v>
       </c>
@@ -2951,7 +2950,7 @@
         <v>4047</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>10</v>
       </c>
@@ -2965,7 +2964,7 @@
         <v>4990</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>11</v>
       </c>
@@ -2979,7 +2978,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
@@ -2993,7 +2992,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
@@ -3010,7 +3009,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>14</v>
       </c>
@@ -3039,7 +3038,7 @@
         <v>-191794</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -3060,7 +3059,7 @@
         <v>0.17830274364642779</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>15</v>
       </c>
@@ -3089,13 +3088,13 @@
         <v>5.2006752009322574E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
     </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>16</v>
       </c>
@@ -3109,7 +3108,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>17</v>
       </c>
@@ -3123,7 +3122,7 @@
         <v>-96114</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>18</v>
       </c>
@@ -3137,7 +3136,7 @@
         <v>95939</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>19</v>
       </c>
@@ -3151,7 +3150,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -3160,7 +3159,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>20</v>
       </c>
@@ -3189,7 +3188,7 @@
         <v>6669.7580645161288</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>21</v>
       </c>
@@ -3218,7 +3217,7 @@
         <v>1.4993047578743728E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>22</v>
       </c>
@@ -3247,7 +3246,7 @@
         <v>284801</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -3268,7 +3267,7 @@
         <v>5.5332159070178468</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>23</v>
       </c>
@@ -3282,7 +3281,7 @@
         <v>106743</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>24</v>
       </c>
@@ -3296,7 +3295,7 @@
         <v>126576</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>25</v>
       </c>
@@ -3310,13 +3309,13 @@
         <v>233412</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
     </row>
-    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>26</v>
       </c>
@@ -3330,13 +3329,13 @@
         <v>413525</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>27</v>
       </c>
@@ -3350,7 +3349,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -3359,7 +3358,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>28</v>
       </c>
@@ -3388,7 +3387,7 @@
         <v>6.2072129164451916E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>30</v>
       </c>
@@ -3417,7 +3416,7 @@
         <v>0.10319013631042701</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>32</v>
       </c>
@@ -3446,7 +3445,7 @@
         <v>7.4872197385235052E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>34</v>
       </c>
@@ -3475,7 +3474,7 @@
         <v>49.937944231821497</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>36</v>
       </c>
@@ -3504,7 +3503,7 @@
         <v>2.1849122035802377</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>37</v>
       </c>
@@ -3518,13 +3517,13 @@
         <v>147405.15254237293</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
       <c r="D46" s="15"/>
     </row>
-    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>38</v>
       </c>
@@ -3538,7 +3537,7 @@
         <v>-46893</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>39</v>
       </c>
@@ -3552,7 +3551,7 @@
         <v>-26139</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>40</v>
       </c>
@@ -3566,7 +3565,7 @@
         <v>-22902</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>41</v>
       </c>
@@ -3580,13 +3579,13 @@
         <v>51471.152542372933</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
       <c r="D51" s="15"/>
     </row>
-    <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>42</v>
       </c>
@@ -3600,7 +3599,7 @@
         <v>-10353</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>43</v>
       </c>
@@ -3614,7 +3613,7 @@
         <v>-23145</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>44</v>
       </c>
@@ -3628,13 +3627,13 @@
         <v>17973.152542372933</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
       <c r="D55" s="15"/>
     </row>
-    <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>45</v>
       </c>
@@ -3648,7 +3647,7 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>46</v>
       </c>
@@ -3662,7 +3661,7 @@
         <v>-35624</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>47</v>
       </c>
@@ -3676,7 +3675,7 @@
         <v>3169.1525423729327</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>48</v>
       </c>
@@ -3690,7 +3689,7 @@
         <v>-73</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>49</v>
       </c>
@@ -3704,951 +3703,951 @@
         <v>3096.1525423729327</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
       <c r="D61" s="15"/>
     </row>
-    <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4656,21 +4655,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.5546875" customWidth="1"/>
-    <col min="2" max="4" width="12.5546875" customWidth="1"/>
-    <col min="5" max="5" width="2.44140625" customWidth="1"/>
-    <col min="6" max="6" width="38.109375" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" customWidth="1"/>
-    <col min="10" max="26" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="39.5703125" customWidth="1"/>
+    <col min="2" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="2.42578125" customWidth="1"/>
+    <col min="6" max="6" width="38.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1">
         <v>2017</v>
@@ -4704,7 +4703,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -4718,7 +4717,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -4727,7 +4726,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
@@ -4757,7 +4756,7 @@
       </c>
       <c r="J5" s="23"/>
     </row>
-    <row r="6" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
@@ -4787,7 +4786,7 @@
       </c>
       <c r="J6" s="23"/>
     </row>
-    <row r="7" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
@@ -4817,7 +4816,7 @@
       </c>
       <c r="J7" s="23"/>
     </row>
-    <row r="8" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -4847,7 +4846,7 @@
       </c>
       <c r="J8" s="23"/>
     </row>
-    <row r="9" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>5</v>
       </c>
@@ -4861,13 +4860,13 @@
         <v>371907</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
     </row>
-    <row r="11" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
@@ -4881,7 +4880,7 @@
         <v>26951</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>7</v>
       </c>
@@ -4895,7 +4894,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
@@ -4909,7 +4908,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>9</v>
       </c>
@@ -4923,7 +4922,7 @@
         <v>4047</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>10</v>
       </c>
@@ -4937,7 +4936,7 @@
         <v>4990</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>11</v>
       </c>
@@ -4951,7 +4950,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
@@ -4965,7 +4964,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
@@ -4982,7 +4981,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>14</v>
       </c>
@@ -5011,7 +5010,7 @@
         <v>-191794</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -5032,7 +5031,7 @@
         <v>0.17830274364642779</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>15</v>
       </c>
@@ -5062,7 +5061,7 @@
       </c>
       <c r="J21" s="25"/>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -5071,7 +5070,7 @@
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>16</v>
       </c>
@@ -5088,7 +5087,7 @@
       <c r="H23" s="26"/>
       <c r="I23" s="26"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>17</v>
       </c>
@@ -5105,7 +5104,7 @@
       <c r="H24" s="26"/>
       <c r="I24" s="26"/>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>18</v>
       </c>
@@ -5122,7 +5121,7 @@
       <c r="H25" s="26"/>
       <c r="I25" s="26"/>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>19</v>
       </c>
@@ -5139,7 +5138,7 @@
       <c r="H26" s="26"/>
       <c r="I26" s="26"/>
     </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -5151,7 +5150,7 @@
       <c r="H27" s="26"/>
       <c r="I27" s="26"/>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>20</v>
       </c>
@@ -5180,7 +5179,7 @@
         <v>6669.7580645161288</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>21</v>
       </c>
@@ -5209,7 +5208,7 @@
         <v>1.4993047578743728E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>22</v>
       </c>
@@ -5238,7 +5237,7 @@
         <v>284801</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -5259,7 +5258,7 @@
         <v>5.5332159070178468</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>23</v>
       </c>
@@ -5276,7 +5275,7 @@
       <c r="H32" s="26"/>
       <c r="I32" s="26"/>
     </row>
-    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>24</v>
       </c>
@@ -5293,7 +5292,7 @@
       <c r="H33" s="26"/>
       <c r="I33" s="26"/>
     </row>
-    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>25</v>
       </c>
@@ -5310,7 +5309,7 @@
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>
     </row>
-    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -5319,7 +5318,7 @@
       <c r="H35" s="26"/>
       <c r="I35" s="26"/>
     </row>
-    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>26</v>
       </c>
@@ -5336,7 +5335,7 @@
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
     </row>
-    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -5345,7 +5344,7 @@
       <c r="H37" s="26"/>
       <c r="I37" s="26"/>
     </row>
-    <row r="38" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>27</v>
       </c>
@@ -5362,7 +5361,7 @@
       <c r="H38" s="26"/>
       <c r="I38" s="26"/>
     </row>
-    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -5374,7 +5373,7 @@
       <c r="H39" s="26"/>
       <c r="I39" s="26"/>
     </row>
-    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>28</v>
       </c>
@@ -5403,7 +5402,7 @@
         <v>6.2072129164451916E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>30</v>
       </c>
@@ -5432,7 +5431,7 @@
         <v>0.10319013631042701</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>32</v>
       </c>
@@ -5461,7 +5460,7 @@
         <v>7.4872197385235052E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>34</v>
       </c>
@@ -5490,7 +5489,7 @@
         <v>49.937944231821497</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>36</v>
       </c>
@@ -5507,7 +5506,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>37</v>
       </c>
@@ -5521,13 +5520,13 @@
         <v>147405.15254237293</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
       <c r="D46" s="15"/>
     </row>
-    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>38</v>
       </c>
@@ -5541,7 +5540,7 @@
         <v>-46893</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>39</v>
       </c>
@@ -5555,7 +5554,7 @@
         <v>-26139</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>40</v>
       </c>
@@ -5569,7 +5568,7 @@
         <v>-22902</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>41</v>
       </c>
@@ -5583,13 +5582,13 @@
         <v>51471.152542372933</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
       <c r="D51" s="15"/>
     </row>
-    <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>42</v>
       </c>
@@ -5603,7 +5602,7 @@
         <v>-10353</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>43</v>
       </c>
@@ -5617,7 +5616,7 @@
         <v>-23145</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>44</v>
       </c>
@@ -5631,7 +5630,7 @@
         <v>17973.152542372933</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -5639,7 +5638,7 @@
       <c r="F55" s="14"/>
       <c r="G55" s="14"/>
     </row>
-    <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>45</v>
       </c>
@@ -5655,7 +5654,7 @@
       <c r="F56" s="14"/>
       <c r="G56" s="14"/>
     </row>
-    <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>46</v>
       </c>
@@ -5669,7 +5668,7 @@
         <v>-35624</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>47</v>
       </c>
@@ -5683,7 +5682,7 @@
         <v>3169.1525423729327</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>48</v>
       </c>
@@ -5697,7 +5696,7 @@
         <v>-73</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>49</v>
       </c>
@@ -5714,951 +5713,951 @@
         <v>3096.1525423729327</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
       <c r="D61" s="15"/>
     </row>
-    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/skillbox/2.6 Case Filled.xlsx
+++ b/skillbox/2.6 Case Filled.xlsx
@@ -20,7 +20,7 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="Z3xi6G1BNgeSwbgbfDU4Hn2WKVhro2ChGy2Be3b4kcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="" roundtripDataChecksum="Z3xi6G1BNgeSwbgbfDU4Hn2WKVhro2ChGy2Be3b4kcw="/>
     </ext>
   </extLst>
 </workbook>
@@ -1424,7 +1424,7 @@
       <c r="D41" s="15">
         <v>-351394</v>
       </c>
-      <c r="F41" s="20" t="s">
+      <c r="F41" t="s">
         <v>31</v>
       </c>
       <c r="G41" s="19">
@@ -1482,7 +1482,7 @@
       <c r="D43" s="8">
         <v>-85357</v>
       </c>
-      <c r="F43" s="20" t="s">
+      <c r="F43" t="s">
         <v>35</v>
       </c>
       <c r="G43" s="19">

--- a/skillbox/2.6 Case Filled.xlsx
+++ b/skillbox/2.6 Case Filled.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\economics\udemy_economics\skillbox\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88991375-C74C-46A6-B39B-B79521A5C576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14505" yWindow="-15" windowWidth="14310" windowHeight="6420"/>
+    <workbookView xWindow="28680" yWindow="270" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1 (2)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -278,7 +289,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -417,8 +428,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="33">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -452,7 +463,6 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -485,7 +495,7 @@
     <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -700,7 +710,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1575,7 +1585,7 @@
         <v>-26139</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>40</v>
       </c>
@@ -1589,7 +1599,7 @@
         <v>-22902</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>41</v>
       </c>
@@ -1602,18 +1612,18 @@
       <c r="D50" s="11">
         <v>51471.152542372933</v>
       </c>
-      <c r="F50" s="33">
+      <c r="J50" s="32">
         <f>B40+B41+B47+B48+B49</f>
         <v>-44626.932203389821</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
       <c r="D51" s="15"/>
     </row>
-    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>42</v>
       </c>
@@ -1627,7 +1637,7 @@
         <v>-10353</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>43</v>
       </c>
@@ -1641,7 +1651,7 @@
         <v>-23145</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>44</v>
       </c>
@@ -1655,13 +1665,13 @@
         <v>17973.152542372933</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
       <c r="D55" s="15"/>
     </row>
-    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>45</v>
       </c>
@@ -1675,7 +1685,7 @@
         <v>20820</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>46</v>
       </c>
@@ -1689,7 +1699,7 @@
         <v>-35624</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>47</v>
       </c>
@@ -1703,7 +1713,7 @@
         <v>3169.1525423729327</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>48</v>
       </c>
@@ -1717,7 +1727,7 @@
         <v>-73</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>49</v>
       </c>
@@ -1731,15 +1741,15 @@
         <v>3096.1525423729327</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
       <c r="D61" s="15"/>
     </row>
-    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2683,7 +2693,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2771,7 +2781,7 @@
       <c r="D5" s="8">
         <v>0</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="20" t="s">
         <v>51</v>
       </c>
       <c r="G5" s="9">
@@ -2800,7 +2810,7 @@
       <c r="D6" s="8">
         <v>188542</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="20" t="s">
         <v>52</v>
       </c>
       <c r="G6" s="9">
@@ -2829,7 +2839,7 @@
       <c r="D7" s="8">
         <v>167750</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="20" t="s">
         <v>53</v>
       </c>
       <c r="G7" s="9">
@@ -2858,7 +2868,7 @@
       <c r="D8" s="8">
         <v>15615</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="20" t="s">
         <v>54</v>
       </c>
       <c r="G8" s="9">
@@ -3022,7 +3032,7 @@
       <c r="D19" s="11">
         <v>41618</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="20" t="s">
         <v>56</v>
       </c>
       <c r="G19" s="14">
@@ -3043,7 +3053,7 @@
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="20" t="s">
         <v>57</v>
       </c>
       <c r="G20" s="9">
@@ -3072,7 +3082,7 @@
       <c r="D21" s="17">
         <v>413525</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="20" t="s">
         <v>58</v>
       </c>
       <c r="G21" s="9">
@@ -3172,7 +3182,7 @@
       <c r="D28" s="8">
         <v>178058</v>
       </c>
-      <c r="F28" s="21" t="s">
+      <c r="F28" s="20" t="s">
         <v>60</v>
       </c>
       <c r="G28" s="18">
@@ -3201,7 +3211,7 @@
       <c r="D29" s="8">
         <v>1993</v>
       </c>
-      <c r="F29" s="21" t="s">
+      <c r="F29" s="20" t="s">
         <v>61</v>
       </c>
       <c r="G29" s="19">
@@ -3230,7 +3240,7 @@
       <c r="D30" s="11">
         <v>180051</v>
       </c>
-      <c r="F30" s="21" t="s">
+      <c r="F30" s="20" t="s">
         <v>62</v>
       </c>
       <c r="G30" s="14">
@@ -3251,7 +3261,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
-      <c r="F31" s="21" t="s">
+      <c r="F31" s="20" t="s">
         <v>63</v>
       </c>
       <c r="G31" s="9">
@@ -3371,7 +3381,7 @@
       <c r="D40" s="8">
         <v>498799.15254237293</v>
       </c>
-      <c r="F40" s="21" t="s">
+      <c r="F40" s="20" t="s">
         <v>65</v>
       </c>
       <c r="G40" s="19">
@@ -3400,7 +3410,7 @@
       <c r="D41" s="15">
         <v>-351394</v>
       </c>
-      <c r="F41" s="21" t="s">
+      <c r="F41" s="20" t="s">
         <v>66</v>
       </c>
       <c r="G41" s="19">
@@ -3429,7 +3439,7 @@
       <c r="D42" s="8">
         <v>-204735</v>
       </c>
-      <c r="F42" s="21" t="s">
+      <c r="F42" s="20" t="s">
         <v>67</v>
       </c>
       <c r="G42" s="19">
@@ -3458,7 +3468,7 @@
       <c r="D43" s="8">
         <v>-85357</v>
       </c>
-      <c r="F43" s="21" t="s">
+      <c r="F43" s="20" t="s">
         <v>68</v>
       </c>
       <c r="G43" s="19">
@@ -3487,7 +3497,7 @@
       <c r="D44" s="8">
         <v>-61302</v>
       </c>
-      <c r="F44" s="21" t="s">
+      <c r="F44" s="20" t="s">
         <v>69</v>
       </c>
       <c r="G44" s="9">
@@ -4655,7 +4665,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4739,22 +4749,22 @@
       <c r="D5" s="8">
         <v>0</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="21">
         <f t="shared" ref="G5:I5" si="0">B14/B40*365</f>
         <v>56.509768268844084</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="21">
         <f t="shared" si="0"/>
         <v>27.954386483020677</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="21">
         <f t="shared" si="0"/>
         <v>2.9614224331997354</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="22"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -4769,22 +4779,22 @@
       <c r="D6" s="8">
         <v>188542</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="21">
         <f t="shared" ref="G6:I6" si="1">(B11+B12+B13)/B40*365</f>
         <v>28.283936681881571</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="21">
         <f t="shared" si="1"/>
         <v>19.219517289237935</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="21">
         <f t="shared" si="1"/>
         <v>21.571478109289597</v>
       </c>
-      <c r="J6" s="23"/>
+      <c r="J6" s="22"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
@@ -4799,22 +4809,22 @@
       <c r="D7" s="8">
         <v>167750</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="21">
         <f t="shared" ref="G7:I7" si="2">B33/B40*365</f>
         <v>45.940622400407264</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <f t="shared" si="2"/>
         <v>55.849769918500165</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="21">
         <f t="shared" si="2"/>
         <v>92.622932024880086</v>
       </c>
-      <c r="J7" s="23"/>
+      <c r="J7" s="22"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
@@ -4829,22 +4839,22 @@
       <c r="D8" s="8">
         <v>15615</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="21">
         <f t="shared" ref="G8:I8" si="3">B40/B9</f>
         <v>3.5005841769341819</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="21">
         <f t="shared" si="3"/>
         <v>2.1577291860085284</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="21">
         <f t="shared" si="3"/>
         <v>1.3411932352506755</v>
       </c>
-      <c r="J8" s="23"/>
+      <c r="J8" s="22"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
@@ -4994,18 +5004,18 @@
       <c r="D19" s="11">
         <v>41618</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G19" s="24">
-        <f t="shared" ref="G19:I19" si="4">B19-B34</f>
+      <c r="G19" s="23">
+        <f>B19-B34</f>
         <v>77916</v>
       </c>
-      <c r="H19" s="24">
-        <f t="shared" si="4"/>
+      <c r="H19" s="23">
+        <f t="shared" ref="H19:I19" si="4">C19-C34</f>
         <v>-87185</v>
       </c>
-      <c r="I19" s="24">
+      <c r="I19" s="23">
         <f t="shared" si="4"/>
         <v>-191794</v>
       </c>
@@ -5015,19 +5025,19 @@
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="25">
-        <f t="shared" ref="G20:I20" si="5">B19/B34</f>
+      <c r="G20" s="24">
+        <f>B19/B34</f>
         <v>1.4337099916504314</v>
       </c>
-      <c r="H20" s="25">
-        <f t="shared" si="5"/>
+      <c r="H20" s="24">
+        <f>C19/C34</f>
         <v>0.59303085468888572</v>
       </c>
-      <c r="I20" s="25">
-        <f t="shared" si="5"/>
+      <c r="I20" s="24">
+        <f>D19/D34</f>
         <v>0.17830274364642779</v>
       </c>
     </row>
@@ -5044,31 +5054,31 @@
       <c r="D21" s="17">
         <v>413525</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="25">
-        <f t="shared" ref="G21:I21" si="6">(B17+B16+B14)/B34</f>
+      <c r="G21" s="24">
+        <f>(B17+B16+B14)/B34</f>
         <v>0.76243250765377124</v>
       </c>
-      <c r="H21" s="25">
-        <f t="shared" si="6"/>
+      <c r="H21" s="24">
+        <f>(C17+C16+C14)/C34</f>
         <v>0.28275685011436308</v>
       </c>
-      <c r="I21" s="25">
-        <f t="shared" si="6"/>
+      <c r="I21" s="24">
+        <f>(D17+D16+D14)/D34</f>
         <v>2.5350024848765272E-2</v>
       </c>
-      <c r="J21" s="25"/>
+      <c r="J21" s="24"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -5083,9 +5093,9 @@
       <c r="D23" s="8">
         <v>237</v>
       </c>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
@@ -5100,9 +5110,9 @@
       <c r="D24" s="8">
         <v>-96114</v>
       </c>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
@@ -5117,9 +5127,9 @@
       <c r="D25" s="8">
         <v>95939</v>
       </c>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
@@ -5134,9 +5144,9 @@
       <c r="D26" s="11">
         <v>62</v>
       </c>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
@@ -5146,9 +5156,9 @@
       <c r="F27" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
@@ -5163,19 +5173,19 @@
       <c r="D28" s="8">
         <v>178058</v>
       </c>
-      <c r="F28" s="21" t="s">
+      <c r="F28" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G28" s="27">
-        <f t="shared" ref="G28:I28" si="7">B21/B26</f>
+      <c r="G28" s="26">
+        <f t="shared" ref="G28:I28" si="5">B21/B26</f>
         <v>16.515705254839983</v>
       </c>
-      <c r="H28" s="27">
-        <f t="shared" si="7"/>
+      <c r="H28" s="26">
+        <f t="shared" si="5"/>
         <v>113.41912464319695</v>
       </c>
-      <c r="I28" s="27">
-        <f t="shared" si="7"/>
+      <c r="I28" s="26">
+        <f t="shared" si="5"/>
         <v>6669.7580645161288</v>
       </c>
     </row>
@@ -5192,19 +5202,19 @@
       <c r="D29" s="8">
         <v>1993</v>
       </c>
-      <c r="F29" s="21" t="s">
+      <c r="F29" s="20" t="s">
         <v>61</v>
       </c>
       <c r="G29" s="19">
-        <f t="shared" ref="G29:I29" si="8">B26/B36</f>
+        <f t="shared" ref="G29:I29" si="6">B26/B36</f>
         <v>6.0548428575700489E-2</v>
       </c>
       <c r="H29" s="19">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>8.8168552097883032E-3</v>
       </c>
       <c r="I29" s="19">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.4993047578743728E-4</v>
       </c>
     </row>
@@ -5221,19 +5231,19 @@
       <c r="D30" s="11">
         <v>180051</v>
       </c>
-      <c r="F30" s="21" t="s">
+      <c r="F30" s="20" t="s">
         <v>62</v>
       </c>
       <c r="G30" s="14">
-        <f t="shared" ref="G30:I30" si="9">B28+B32</f>
+        <f t="shared" ref="G30:I30" si="7">B28+B32</f>
         <v>361310</v>
       </c>
       <c r="H30" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>355590</v>
       </c>
       <c r="I30" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>284801</v>
       </c>
     </row>
@@ -5242,19 +5252,19 @@
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
-      <c r="F31" s="21" t="s">
+      <c r="F31" s="20" t="s">
         <v>63</v>
       </c>
       <c r="G31" s="9">
-        <f t="shared" ref="G31:I31" si="10">G30/B50</f>
+        <f t="shared" ref="G31:I31" si="8">G30/B50</f>
         <v>-8.0962320769285423</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>12.056849306408786</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>5.5332159070178468</v>
       </c>
     </row>
@@ -5271,9 +5281,9 @@
       <c r="D32" s="8">
         <v>106743</v>
       </c>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
     </row>
     <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
@@ -5288,9 +5298,9 @@
       <c r="D33" s="8">
         <v>126576</v>
       </c>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
     </row>
     <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
@@ -5305,18 +5315,18 @@
       <c r="D34" s="11">
         <v>233412</v>
       </c>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
     </row>
     <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
     </row>
     <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
@@ -5331,18 +5341,18 @@
       <c r="D36" s="17">
         <v>413525</v>
       </c>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
     </row>
     <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
     </row>
     <row r="38" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
@@ -5357,9 +5367,9 @@
       <c r="D38" s="4">
         <v>2019</v>
       </c>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
     </row>
     <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
@@ -5369,9 +5379,9 @@
       <c r="F39" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
     </row>
     <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
@@ -5386,19 +5396,19 @@
       <c r="D40" s="8">
         <v>498799.15254237293</v>
       </c>
-      <c r="F40" s="21" t="s">
+      <c r="F40" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="G40" s="28">
-        <f t="shared" ref="G40:I40" si="11">B60/B40</f>
+      <c r="G40" s="27">
+        <f t="shared" ref="G40:I40" si="9">B60/B40</f>
         <v>-4.9301461594820926E-2</v>
       </c>
-      <c r="H40" s="28">
-        <f t="shared" si="11"/>
+      <c r="H40" s="27">
+        <f t="shared" si="9"/>
         <v>-2.466550035146654E-2</v>
       </c>
-      <c r="I40" s="28">
-        <f t="shared" si="11"/>
+      <c r="I40" s="27">
+        <f t="shared" si="9"/>
         <v>6.2072129164451916E-3</v>
       </c>
     </row>
@@ -5415,19 +5425,19 @@
       <c r="D41" s="15">
         <v>-351394</v>
       </c>
-      <c r="F41" s="21" t="s">
+      <c r="F41" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="G41" s="28">
-        <f t="shared" ref="G41:I41" si="12">B50/B40</f>
+      <c r="G41" s="27">
+        <f t="shared" ref="G41:I41" si="10">B50/B40</f>
         <v>-5.2237150113293378E-2</v>
       </c>
-      <c r="H41" s="28">
-        <f t="shared" si="12"/>
+      <c r="H41" s="27">
+        <f t="shared" si="10"/>
         <v>3.9078461272421504E-2</v>
       </c>
-      <c r="I41" s="28">
-        <f t="shared" si="12"/>
+      <c r="I41" s="27">
+        <f t="shared" si="10"/>
         <v>0.10319013631042701</v>
       </c>
     </row>
@@ -5444,19 +5454,19 @@
       <c r="D42" s="8">
         <v>-204735</v>
       </c>
-      <c r="F42" s="21" t="s">
+      <c r="F42" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="G42" s="29">
-        <f t="shared" ref="G42:I42" si="13">B60/B21</f>
+      <c r="G42" s="28">
+        <f t="shared" ref="G42:I42" si="11">B60/B21</f>
         <v>-8.3966652120430654E-2</v>
       </c>
-      <c r="H42" s="29">
-        <f t="shared" si="13"/>
+      <c r="H42" s="28">
+        <f t="shared" si="11"/>
         <v>-3.9040842632521271E-2</v>
       </c>
-      <c r="I42" s="29">
-        <f t="shared" si="13"/>
+      <c r="I42" s="28">
+        <f t="shared" si="11"/>
         <v>7.4872197385235052E-3</v>
       </c>
     </row>
@@ -5473,19 +5483,19 @@
       <c r="D43" s="8">
         <v>-85357</v>
       </c>
-      <c r="F43" s="21" t="s">
+      <c r="F43" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G43" s="30">
-        <f t="shared" ref="G43:I43" si="14">B60/B26</f>
+      <c r="G43" s="29">
+        <f t="shared" ref="G43:I43" si="12">B60/B26</f>
         <v>-1.3867684776567173</v>
       </c>
-      <c r="H43" s="30">
-        <f t="shared" si="14"/>
+      <c r="H43" s="29">
+        <f t="shared" si="12"/>
         <v>-4.4279781967133669</v>
       </c>
-      <c r="I43" s="30">
-        <f t="shared" si="14"/>
+      <c r="I43" s="29">
+        <f t="shared" si="12"/>
         <v>49.937944231821497</v>
       </c>
     </row>
@@ -5502,7 +5512,7 @@
       <c r="D44" s="8">
         <v>-61302</v>
       </c>
-      <c r="F44" s="21" t="s">
+      <c r="F44" s="20" t="s">
         <v>69</v>
       </c>
     </row>
@@ -5572,13 +5582,13 @@
       <c r="A50" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="31">
+      <c r="B50" s="30">
         <v>-44626.932203389821</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="30">
         <v>29492.779661017004</v>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="30">
         <v>51471.152542372933</v>
       </c>
     </row>
@@ -5592,13 +5602,13 @@
       <c r="A52" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="32">
+      <c r="B52" s="31">
         <v>-7540</v>
       </c>
-      <c r="C52" s="32">
+      <c r="C52" s="31">
         <v>-13580</v>
       </c>
-      <c r="D52" s="32">
+      <c r="D52" s="31">
         <v>-10353</v>
       </c>
     </row>
@@ -5606,13 +5616,13 @@
       <c r="A53" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="32">
+      <c r="B53" s="31">
         <v>-32802</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="31">
         <v>-25487</v>
       </c>
-      <c r="D53" s="32">
+      <c r="D53" s="31">
         <v>-23145</v>
       </c>
     </row>
@@ -5642,13 +5652,13 @@
       <c r="A56" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B56" s="32">
+      <c r="B56" s="31">
         <v>131858</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="31">
         <v>34570</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="31">
         <v>20820</v>
       </c>
       <c r="F56" s="14"/>
@@ -5658,13 +5668,13 @@
       <c r="A57" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="31">
         <v>-89000</v>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="31">
         <v>-43582</v>
       </c>
-      <c r="D57" s="32">
+      <c r="D57" s="31">
         <v>-35624</v>
       </c>
     </row>
@@ -5686,13 +5696,13 @@
       <c r="A59" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B59" s="32">
+      <c r="B59" s="31">
         <v>-8</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="31">
         <v>-29</v>
       </c>
-      <c r="D59" s="32">
+      <c r="D59" s="31">
         <v>-73</v>
       </c>
     </row>
@@ -5701,15 +5711,15 @@
         <v>49</v>
       </c>
       <c r="B60" s="11">
-        <f t="shared" ref="B60:D60" si="15">B50+B52+B53+B56+B57+B59</f>
+        <f t="shared" ref="B60:D60" si="13">B50+B52+B53+B56+B57+B59</f>
         <v>-42118.932203389821</v>
       </c>
       <c r="C60" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-18615.220338982996</v>
       </c>
       <c r="D60" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>3096.1525423729327</v>
       </c>
     </row>
